--- a/outputs/daily/hr_rankings_2026-07-21.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-21.xlsx
@@ -68139,27 +68139,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-21T23:40:00Z</t>
+          <t>2026-07-21T22:40:00Z</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -68169,26 +68169,26 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -68202,26 +68202,26 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P247" t="n">
-        <v>18.1</v>
+        <v>23.7</v>
       </c>
       <c r="Q247" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="R247" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S247" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T247" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U247" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="V247" t="inlineStr">
         <is>
@@ -68235,7 +68235,7 @@
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -68277,12 +68277,12 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
@@ -68292,12 +68292,12 @@
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 9.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.5% barrel, 8.2 HR allowed</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -68307,104 +68307,104 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>96.934</t>
+          <t>98.9857</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>0.3576</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.2752</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>73.45</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>31.97</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>0.4032</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="BE247" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1177</t>
         </is>
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>21.68</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr"/>
       <c r="BH247" t="inlineStr"/>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr"/>
@@ -68415,12 +68415,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -68445,7 +68445,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -68464,7 +68464,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -68482,22 +68482,22 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>23.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q248" t="n">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="R248" t="n">
         <v>27.6</v>
       </c>
       <c r="S248" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T248" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U248" t="n">
-        <v>7</v>
+        <v>25.8</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -68553,12 +68553,12 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -68568,12 +68568,12 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.5% barrel, 8.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.5% barrel, 8.2 HR allowed</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
@@ -68583,67 +68583,67 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>98.9857</t>
+          <t>97.4605</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>0.2752</t>
+          <t>0.2806</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>73.45</t>
+          <t>69.99</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
@@ -68691,27 +68691,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-21T22:40:00Z</t>
+          <t>2026-07-21T23:40:00Z</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -68726,17 +68726,17 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L249" t="n">
@@ -68754,26 +68754,26 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="Q249" t="n">
-        <v>19.1</v>
+        <v>36.4</v>
       </c>
       <c r="R249" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S249" t="n">
         <v>47.9</v>
       </c>
       <c r="T249" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U249" t="n">
-        <v>25.8</v>
+        <v>7</v>
       </c>
       <c r="V249" t="inlineStr">
         <is>
@@ -68829,7 +68829,7 @@
       </c>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI249" t="inlineStr">
@@ -68844,12 +68844,12 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.5% barrel, 8.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 9.9 HR allowed</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
@@ -68859,104 +68859,104 @@
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>97.4605</t>
+          <t>96.934</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3576</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>0.2806</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>69.99</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.4032</t>
         </is>
       </c>
       <c r="BE249" t="inlineStr">
         <is>
-          <t>0.1177</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr"/>
       <c r="BH249" t="inlineStr"/>
       <c r="BI249" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ249" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-07-21.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-21.xlsx
@@ -12842,34 +12842,30 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -19238,34 +19234,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -20358,34 +20350,30 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -21754,34 +21742,30 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -23152,28 +23136,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -24834,34 +24822,30 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -51890,34 +51874,30 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -53006,34 +52986,30 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -55474,34 +55450,30 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
